--- a/themen_und_ansprechpersonen.xlsx
+++ b/themen_und_ansprechpersonen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lroesele.IVV5NET\sciebo - Röseler, Lukas (lroesele@uni-muenster.de)@uni-muenster.sciebo.de\LeaRn\MueCOS-Infomodule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE80C363-916F-429C-819C-C0DCA7CDCECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B948839-5495-49AE-8C59-7E7341FC56F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC10942A-3D47-4CC2-9B6B-6AB99B47D6AE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC10942A-3D47-4CC2-9B6B-6AB99B47D6AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="108">
   <si>
     <t>0. Übergreifend</t>
   </si>
@@ -674,7 +677,7 @@
     <tableColumn id="5" xr3:uid="{FF24ED07-6D5F-4A6A-8DC3-E86488692DEA}" name="Ansprechperson" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{1227DF38-4210-4874-82CD-A7AD5412B899}" name="Website" dataDxfId="0" dataCellStyle="Link"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1093,8 +1096,12 @@
       <c r="B6" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>91</v>
       </c>
@@ -1538,7 +1545,9 @@
       <c r="E28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
